--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26024"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26111"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1113" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F32E5B6-3B85-4127-87A0-AFBA77DD00BC}"/>
+  <xr:revisionPtr revIDLastSave="1118" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44A23581-4DE5-4221-A490-77D52D3C5A35}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1559,6 +1559,9 @@
       <c r="C73" s="4">
         <v>44925</v>
       </c>
+      <c r="D73" s="4">
+        <v>44939</v>
+      </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
@@ -1570,6 +1573,9 @@
       <c r="C74" s="6">
         <v>-161000</v>
       </c>
+      <c r="D74" s="6">
+        <v>15000</v>
+      </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="3" t="s">
@@ -1581,6 +1587,9 @@
       <c r="C75" s="7">
         <v>660000</v>
       </c>
+      <c r="D75" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
@@ -1592,6 +1601,9 @@
       <c r="C76" s="6">
         <v>622000</v>
       </c>
+      <c r="D76" s="6">
+        <v>39000</v>
+      </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="3" t="s">
@@ -1604,6 +1616,10 @@
       <c r="C77" s="8">
         <f>C74+C75-C76</f>
         <v>-123000</v>
+      </c>
+      <c r="D77" s="8">
+        <f>D74+D75-D76</f>
+        <v>-24000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26111"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1118" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44A23581-4DE5-4221-A490-77D52D3C5A35}"/>
+  <xr:revisionPtr revIDLastSave="1122" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A238012E-EC84-4872-87AD-57521B861E45}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1562,6 +1562,9 @@
       <c r="D73" s="4">
         <v>44939</v>
       </c>
+      <c r="E73" s="4">
+        <v>44946</v>
+      </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
@@ -1576,6 +1579,9 @@
       <c r="D74" s="6">
         <v>15000</v>
       </c>
+      <c r="E74" s="6">
+        <v>-25000</v>
+      </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="3" t="s">
@@ -1590,6 +1596,9 @@
       <c r="D75" s="7">
         <v>0</v>
       </c>
+      <c r="E75" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
@@ -1604,6 +1613,9 @@
       <c r="D76" s="6">
         <v>39000</v>
       </c>
+      <c r="E76" s="6">
+        <v>43000</v>
+      </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="3" t="s">
@@ -1620,6 +1632,10 @@
       <c r="D77" s="8">
         <f>D74+D75-D76</f>
         <v>-24000</v>
+      </c>
+      <c r="E77" s="8">
+        <f>E74+E75-E76</f>
+        <v>-68000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26125"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1122" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A238012E-EC84-4872-87AD-57521B861E45}"/>
+  <xr:revisionPtr revIDLastSave="1126" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{056884F8-55F6-4E44-902F-F9A61EF698C9}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="5">
   <si>
     <t>Date</t>
   </si>
@@ -436,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1638,6 +1638,47 @@
         <v>-68000</v>
       </c>
     </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B79" s="4">
+        <v>44946</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="6">
+        <v>-74000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B81" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B82" s="6">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B83" s="8">
+        <f>B80+B81-B82</f>
+        <v>-128000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1126" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{056884F8-55F6-4E44-902F-F9A61EF698C9}"/>
+  <xr:revisionPtr revIDLastSave="1130" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF7C9B46-3B54-4753-8F7A-A953913AC069}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1645,6 +1645,9 @@
       <c r="B79" s="4">
         <v>44946</v>
       </c>
+      <c r="C79" s="4">
+        <v>44960</v>
+      </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
@@ -1653,30 +1656,43 @@
       <c r="B80" s="6">
         <v>-74000</v>
       </c>
-    </row>
-    <row r="81" spans="1:2">
+      <c r="C80" s="6">
+        <v>-88000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B81" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:2">
+      <c r="C81" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B82" s="6">
         <v>54000</v>
       </c>
-    </row>
-    <row r="83" spans="1:2">
+      <c r="C82" s="6">
+        <v>105000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B83" s="8">
         <f>B80+B81-B82</f>
         <v>-128000</v>
+      </c>
+      <c r="C83" s="8">
+        <f>C80+C81-C82</f>
+        <v>-193000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26207"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1130" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF7C9B46-3B54-4753-8F7A-A953913AC069}"/>
+  <xr:revisionPtr revIDLastSave="1132" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D86613E-4684-4E2C-BD7C-0913A75EAE25}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1648,6 +1648,9 @@
       <c r="C79" s="4">
         <v>44960</v>
       </c>
+      <c r="D79" s="4">
+        <v>44960</v>
+      </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
@@ -1659,8 +1662,11 @@
       <c r="C80" s="6">
         <v>-88000</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="D80" s="6">
+        <v>-143000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" s="3" t="s">
         <v>2</v>
       </c>
@@ -1670,8 +1676,11 @@
       <c r="C81" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="D81" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" s="3" t="s">
         <v>1</v>
       </c>
@@ -1681,8 +1690,11 @@
       <c r="C82" s="6">
         <v>105000</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="D82" s="6">
+        <v>105000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" s="3" t="s">
         <v>4</v>
       </c>
@@ -1693,6 +1705,10 @@
       <c r="C83" s="8">
         <f>C80+C81-C82</f>
         <v>-193000</v>
+      </c>
+      <c r="D83" s="8">
+        <f>D80+D81-D82</f>
+        <v>-248000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26219"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1132" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D86613E-4684-4E2C-BD7C-0913A75EAE25}"/>
+  <xr:revisionPtr revIDLastSave="1137" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA0760F9-73D3-4809-9107-D1B31C3A51B1}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1651,6 +1651,9 @@
       <c r="D79" s="4">
         <v>44960</v>
       </c>
+      <c r="E79" s="4">
+        <v>44981</v>
+      </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
@@ -1665,8 +1668,11 @@
       <c r="D80" s="6">
         <v>-143000</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="E80" s="6">
+        <v>-159000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" s="3" t="s">
         <v>2</v>
       </c>
@@ -1679,8 +1685,11 @@
       <c r="D81" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="E81" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
         <v>1</v>
       </c>
@@ -1693,8 +1702,11 @@
       <c r="D82" s="6">
         <v>105000</v>
       </c>
-    </row>
-    <row r="83" spans="1:4">
+      <c r="E82" s="6">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" s="3" t="s">
         <v>4</v>
       </c>
@@ -1709,6 +1721,10 @@
       <c r="D83" s="8">
         <f>D80+D81-D82</f>
         <v>-248000</v>
+      </c>
+      <c r="E83" s="8">
+        <f>E80+E81-E82</f>
+        <v>-294000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/06-YTD Profit.xlsx
+++ b/Excel/06-YTD Profit.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26306"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1137" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA0760F9-73D3-4809-9107-D1B31C3A51B1}"/>
+  <xr:revisionPtr revIDLastSave="1146" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F24C6D3C-EC9B-4AE6-97FC-468BEA17E49F}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="5">
   <si>
     <t>Date</t>
   </si>
@@ -436,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1727,6 +1727,63 @@
         <v>-294000</v>
       </c>
     </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B85" s="4">
+        <v>44988</v>
+      </c>
+      <c r="C85" s="4">
+        <v>44995</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="6">
+        <v>-159000</v>
+      </c>
+      <c r="C86" s="6">
+        <v>-174000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B87" s="7">
+        <v>0</v>
+      </c>
+      <c r="C87" s="7">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B88" s="6">
+        <v>140000</v>
+      </c>
+      <c r="C88" s="6">
+        <v>146000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B89" s="8">
+        <f>B86+B87-B88</f>
+        <v>-299000</v>
+      </c>
+      <c r="C89" s="8">
+        <f>C86+C87-C88</f>
+        <v>-304000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
